--- a/data/compare/do-vs-lightsail-catalog.xlsx
+++ b/data/compare/do-vs-lightsail-catalog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DO vs Lightsail" sheetId="1" state="visible" r:id="rId2"/>
@@ -9901,7 +9901,8 @@
   <dimension ref="A1:L894"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="41.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
@@ -39816,453 +39817,456 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="60.4296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="60.42"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>3117</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>3118</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3119</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3121</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3122</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>3123</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>3124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>3125</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>3126</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>3127</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3128</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>3129</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>3130</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>3131</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>3132</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>3133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>3134</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>3135</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>3136</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>3137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>3138</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>3139</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>3140</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>3141</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>3142</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>3143</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>1802</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>3144</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>3145</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>3146</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>3147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>3148</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>3149</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>3150</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>3151</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>3152</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>3153</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>3154</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>3155</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>3156</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>3157</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>1363</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>3158</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>3159</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>3160</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>3161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>3162</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>3163</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>3164</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>3165</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>3166</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>3167</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>3168</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>3169</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>3170</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>3171</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>3172</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>3173</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>3174</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>3175</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>3176</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>3177</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>3178</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>1363</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>3179</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>3180</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>3181</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>3182</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>3183</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>3184</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>3185</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>3186</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>3187</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>3188</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>3189</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>3190</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>3191</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>3192</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>3193</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>3194</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>3195</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>3196</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>3197</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>3198</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>3199</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>3200</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>3201</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>3202</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>3203</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>3204</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>3205</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>3206</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>3207</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>3208</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>3209</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>3210</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>3211</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>3212</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>3213</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>3214</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>3215</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>3216</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>2246</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>3217</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>3218</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>3219</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>3220</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>3221</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>3222</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>2804</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>3223</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>3224</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>3225</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>3226</v>
       </c>
     </row>
